--- a/Sales_Performance.xlsx
+++ b/Sales_Performance.xlsx
@@ -9,10 +9,10 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="20" windowWidth="16100" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="20" windowWidth="16100" windowHeight="7620"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sales_Performance" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
@@ -14106,5 +14106,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>